--- a/quizzes/peinture-20e-niveau1.xlsx
+++ b/quizzes/peinture-20e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B46EEB2-4510-46DC-A7C6-10E730224662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD161647-4ED8-4DBA-A58C-F3414D974229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,9 +280,6 @@
     <t>Composition II en rouge, bleu et jaune</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Kazimir_Malevich%2C_1915%2C_Black_Suprematic_Square%2C_oil_on_linen_canvas%2C_79.5_x_79.5_cm%2C_Tretyakov_Gallery%2C_Moscow.jpg/1280px-Kazimir_Malevich%2C_1915%2C_Black_Suprematic_Square%2C_oil_on_linen_canvas%2C_79.5_x_79.5_cm%2C_Tretyakov_Gallery%2C_Moscow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Kazimir MALEVICH</t>
   </si>
   <si>
@@ -449,6 +446,9 @@
   </si>
   <si>
     <t>Les Footballeurs</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -901,546 +901,549 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
-        <v>104</v>
+      <c r="A23" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1952</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>140</v>
+      <c r="A29" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="7">
-        <v>1952</v>
+        <v>96</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="A30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A29" r:id="rId30" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A27" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A31" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A2" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A25" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A21" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A29" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A4" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A12" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="A8" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A17" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="A23" r:id="rId29" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A19" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E388D481-4878-4695-9178-DAC43682E711}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau1.xlsx
+++ b/quizzes/peinture-20e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD161647-4ED8-4DBA-A58C-F3414D974229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6027E21D-689F-4780-9E30-C64EF1B8F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15615" yWindow="915" windowWidth="15735" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz peinture 20e niveau1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="142">
   <si>
     <t>image</t>
   </si>
@@ -37,9 +37,6 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2c/Ch%C3%AF%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg/1280px-Ch%C3%AF%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Chaïm SOUTINE</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>Le Bœuf écorché</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/44/Self-Portrait_in_Tuxedo.jpg/1280px-Self-Portrait_in_Tuxedo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Max BECKMANN</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Autoportrait en smoking</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg/1280px-Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>André DERAIN</t>
   </si>
   <si>
@@ -82,9 +73,6 @@
     <t>Le Pont de Charing Cross</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/La_Danse_II%2C_par_Henri_Matisse.jpg/1280px-La_Danse_II%2C_par_Henri_Matisse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henri MATISSE</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>Le Baiser</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/1280px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Edvard MUNCH</t>
   </si>
   <si>
@@ -127,9 +112,6 @@
     <t>Le Cri (version de 1910)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Wassily KANDINSKY</t>
   </si>
   <si>
@@ -142,9 +124,6 @@
     <t>Composition 8</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Raoul DUFY</t>
   </si>
   <si>
@@ -157,9 +136,6 @@
     <t>La Fée Électricité</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Ferdinand_hodler%2C_lo_jungfrau_tra_la_nebbia%2C_1908.JPG/1280px-Ferdinand_hodler%2C_lo_jungfrau_tra_la_nebbia%2C_1908.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Ferdinand HODLER</t>
   </si>
   <si>
@@ -172,9 +148,6 @@
     <t>La Jungfrau dans le brouillard</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Mama%2C_Papa_is_Wounded%21.jpg/1280px-Mama%2C_Papa_is_Wounded%21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Yves TANGUY</t>
   </si>
   <si>
@@ -184,9 +157,6 @@
     <t>Maman, Papa est blessé !</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Amedeo MODIGLIANI</t>
   </si>
   <si>
@@ -199,9 +169,6 @@
     <t>Nu couché</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Egon SCHIELE</t>
   </si>
   <si>
@@ -214,18 +181,12 @@
     <t>Autoportrait à la tête baissée</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg/1280px-Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henri ROUSSEAU (Le Douanier)</t>
   </si>
   <si>
     <t>Le Rêve</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg/1280px-Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pavel FILONOV</t>
   </si>
   <si>
@@ -238,9 +199,6 @@
     <t>Formule du prolétariat de Petrograd</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg/1280px-Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pierre BONNARD</t>
   </si>
   <si>
@@ -265,9 +223,6 @@
     <t>La Maison de Berlioz (Montmartre)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Piet MONDRIAN</t>
   </si>
   <si>
@@ -292,33 +247,15 @@
     <t>Carré noir sur fond blanc</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d0/Composition_au_damier_-_Fernand_L%C3%A9ger.jpg/1280px-Composition_au_damier_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Fernand LÉGER</t>
   </si>
   <si>
-    <t>1929</t>
-  </si>
-  <si>
-    <t>Collection privée</t>
-  </si>
-  <si>
-    <t>Composition au damier</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/The_City_Rises_by_Umberto_Boccioni_1910.jpg/1280px-The_City_Rises_by_Umberto_Boccioni_1910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Umberto BOCCIONI</t>
   </si>
   <si>
     <t>La Ville qui monte</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg/1280px-Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Franz MARC</t>
   </si>
   <si>
@@ -331,21 +268,9 @@
     <t>Les Grands Chevaux bleus</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>August MACKE</t>
   </si>
   <si>
-    <t>Museum Ludwig, Cologne</t>
-  </si>
-  <si>
-    <t>Marché de Tunis II</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/85/Robert_delaunay%2C_tour_eiffel%2C_1926.jpg/1280px-Robert_delaunay%2C_tour_eiffel%2C_1926.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Robert DELAUNAY</t>
   </si>
   <si>
@@ -358,9 +283,6 @@
     <t>La Tour Eiffel</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6f/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Juan GRIS</t>
   </si>
   <si>
@@ -370,9 +292,6 @@
     <t>Portrait de Pablo Picasso</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/1280px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>László MOHOLY-NAGY</t>
   </si>
   <si>
@@ -385,9 +304,6 @@
     <t>Composition A.XX</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/The_Two_Fridas.jpg/1280px-The_Two_Fridas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Frida KAHLO</t>
   </si>
   <si>
@@ -400,9 +316,6 @@
     <t>Les Deux Frida</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Grant_Wood_-_American_Gothic_%281930%29.jpg/1280px-Grant_Wood_-_American_Gothic_%281930%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Grant WOOD</t>
   </si>
   <si>
@@ -449,6 +362,90 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Mama%2C_Papa_is_Wounded%21.jpg/960px-Mama%2C_Papa_is_Wounded%21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Grant_Wood_-_American_Gothic_%281930%29.jpg/960px-Grant_Wood_-_American_Gothic_%281930%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/960px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg/1280px-Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Neue Pinakothek, Munich</t>
+  </si>
+  <si>
+    <t>Jeunes filles sous les arbres</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg/1280px-Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/1280px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg/1920px-Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Centre national d’art et de culture Georges-Pompidou du Paris </t>
+  </si>
+  <si>
+    <t>Le Mécanicien</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg/1280px-Franz_Marc_-_Die_gro%C3%9Fen_blauen_Pferde_1911.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Les_Deux_Fridas.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/La_Danse_II%2C_par_Henri_Matisse.jpg/1280px-La_Danse_II%2C_par_Henri_Matisse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg/1280px-Henri_Rousseau_-_Le_R%C3%AAve_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Self-Portrait_in_Tuxedo.jpg/1280px-Self-Portrait_in_Tuxedo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3d/Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg/1280px-Filonov_-_formula-of-the-petrograd-proletariat-1920-21.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg/1280px-Pierre_Bonnard_-_nu_dans_le_bain_%28amvp_2520_554713%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9b/Robert_delaunay%2C_tour_eiffel%2C_1926.jpg/1280px-Robert_delaunay%2C_tour_eiffel%2C_1926.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b4/The_City_Rises_by_Umberto_Boccioni_1910.jpg/1280px-The_City_Rises_by_Umberto_Boccioni_1910.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
@@ -900,513 +897,513 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>54</v>
+      <c r="A2" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
-        <v>45</v>
+      <c r="A9" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
-        <v>90</v>
+      <c r="A10" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1918</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>116</v>
+      <c r="A20" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C23" s="7">
         <v>1952</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>81</v>
+      <c r="A26" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
-        <v>50</v>
+      <c r="A31" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1414,36 +1411,36 @@
     <sortCondition ref="B2:B31"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A27" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A31" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A2" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A25" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A21" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A29" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A4" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A12" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="A8" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A17" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A23" r:id="rId29" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
-    <hyperlink ref="A19" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E388D481-4878-4695-9178-DAC43682E711}"/>
+    <hyperlink ref="A14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A21" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="A23" r:id="rId5" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A19" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E388D481-4878-4695-9178-DAC43682E711}"/>
+    <hyperlink ref="A26" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B0491CE-5878-4284-9EB3-1CAE571073F5}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BA7F6A54-3B55-4CA1-913A-966DED893B72}"/>
+    <hyperlink ref="A31" r:id="rId9" xr:uid="{66617D80-66D1-4204-9086-F48C21B020E0}"/>
+    <hyperlink ref="A13" r:id="rId10" xr:uid="{0E4DF9FA-B9B4-434E-873D-8C7D7FD873BD}"/>
+    <hyperlink ref="A20" r:id="rId11" xr:uid="{98298F60-1A0B-47C9-96A2-DE89B59E8628}"/>
+    <hyperlink ref="A2" r:id="rId12" xr:uid="{464ECBC7-87A7-4781-8C5B-C632AEBADC12}"/>
+    <hyperlink ref="A3" r:id="rId13" xr:uid="{758CF4F1-880C-48E4-A2B1-204679A22EA7}"/>
+    <hyperlink ref="A4" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{37043E81-17E6-42F7-9C6C-3086EC85D278}"/>
+    <hyperlink ref="A5" r:id="rId15" xr:uid="{A03D7D04-CD22-4203-8A15-2313E0EDEA52}"/>
+    <hyperlink ref="A6" r:id="rId16" xr:uid="{90C1B8BD-8BEB-4D69-9EBD-8740E75C8FEB}"/>
+    <hyperlink ref="A7" r:id="rId17" xr:uid="{A1FF0AEB-3C7F-46E9-A2F4-0748EB365A91}"/>
+    <hyperlink ref="A10" r:id="rId18" xr:uid="{D7963678-68E4-4022-A77F-33E8E5E51C37}"/>
+    <hyperlink ref="A11" r:id="rId19" xr:uid="{289B2CD7-ABF1-4282-9EC0-774C92EDE015}"/>
+    <hyperlink ref="A12" r:id="rId20" xr:uid="{F163392F-73C6-430A-8A1B-3883B157121D}"/>
+    <hyperlink ref="A15" r:id="rId21" xr:uid="{F14DB676-86ED-4C4C-A82E-041A41111809}"/>
+    <hyperlink ref="A16" r:id="rId22" xr:uid="{ECD26114-AD89-4911-BC86-BD26FFA12A5B}"/>
+    <hyperlink ref="A18" r:id="rId23" xr:uid="{3DE72F04-773E-4312-BC3A-BAE2854A427A}"/>
+    <hyperlink ref="A22" r:id="rId24" xr:uid="{F455AB80-CB66-43BE-8398-CC28BD4FF81B}"/>
+    <hyperlink ref="A24" r:id="rId25" xr:uid="{83FD4BF5-2358-46C2-8D0C-96072593D040}"/>
+    <hyperlink ref="A25" r:id="rId26" xr:uid="{6507E877-B226-4C5B-8F8F-D66D9332E209}"/>
+    <hyperlink ref="A27" r:id="rId27" xr:uid="{5951487C-03AF-4F1F-8662-2C314FAEDD66}"/>
+    <hyperlink ref="A28" r:id="rId28" xr:uid="{A8221384-A48D-40A8-8C81-AC2AF6C7B442}"/>
+    <hyperlink ref="A29" r:id="rId29" xr:uid="{B97A3276-EC4E-49EA-8E07-10F5C0D21A0F}"/>
+    <hyperlink ref="A30" r:id="rId30" xr:uid="{B0B6F075-9800-4611-AECC-AA4AE46A87D0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau1.xlsx
+++ b/quizzes/peinture-20e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6027E21D-689F-4780-9E30-C64EF1B8F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC9A633-747D-490A-B40B-0D2DB0240212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15615" yWindow="915" windowWidth="15735" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz peinture 20e niveau1" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,6 @@
     <t>Nu dans le bain</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Maurice UTRILLO</t>
   </si>
   <si>
@@ -446,6 +443,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Kandinsky_-_Composition_8%2C_July_1923.jpg/1280px-Kandinsky_-_Composition_8%2C_July_1923.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
@@ -898,7 +898,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>45</v>
@@ -915,7 +915,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>13</v>
@@ -932,24 +932,24 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>5</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>26</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>49</v>
@@ -1000,24 +1000,24 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>38</v>
@@ -1034,70 +1034,70 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="7">
         <v>1918</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>53</v>
@@ -1153,92 +1153,92 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
@@ -1255,24 +1255,24 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="7">
         <v>1952</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>55</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>59</v>
@@ -1306,24 +1306,24 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>34</v>
@@ -1340,27 +1340,27 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>27</v>
@@ -1369,12 +1369,12 @@
         <v>43</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>30</v>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>42</v>
@@ -1412,35 +1412,35 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A21" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A23" r:id="rId5" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
-    <hyperlink ref="A19" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E388D481-4878-4695-9178-DAC43682E711}"/>
-    <hyperlink ref="A26" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B0491CE-5878-4284-9EB3-1CAE571073F5}"/>
-    <hyperlink ref="A9" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BA7F6A54-3B55-4CA1-913A-966DED893B72}"/>
-    <hyperlink ref="A31" r:id="rId9" xr:uid="{66617D80-66D1-4204-9086-F48C21B020E0}"/>
-    <hyperlink ref="A13" r:id="rId10" xr:uid="{0E4DF9FA-B9B4-434E-873D-8C7D7FD873BD}"/>
-    <hyperlink ref="A20" r:id="rId11" xr:uid="{98298F60-1A0B-47C9-96A2-DE89B59E8628}"/>
-    <hyperlink ref="A2" r:id="rId12" xr:uid="{464ECBC7-87A7-4781-8C5B-C632AEBADC12}"/>
-    <hyperlink ref="A3" r:id="rId13" xr:uid="{758CF4F1-880C-48E4-A2B1-204679A22EA7}"/>
-    <hyperlink ref="A4" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{37043E81-17E6-42F7-9C6C-3086EC85D278}"/>
-    <hyperlink ref="A5" r:id="rId15" xr:uid="{A03D7D04-CD22-4203-8A15-2313E0EDEA52}"/>
-    <hyperlink ref="A6" r:id="rId16" xr:uid="{90C1B8BD-8BEB-4D69-9EBD-8740E75C8FEB}"/>
-    <hyperlink ref="A7" r:id="rId17" xr:uid="{A1FF0AEB-3C7F-46E9-A2F4-0748EB365A91}"/>
-    <hyperlink ref="A10" r:id="rId18" xr:uid="{D7963678-68E4-4022-A77F-33E8E5E51C37}"/>
-    <hyperlink ref="A11" r:id="rId19" xr:uid="{289B2CD7-ABF1-4282-9EC0-774C92EDE015}"/>
-    <hyperlink ref="A12" r:id="rId20" xr:uid="{F163392F-73C6-430A-8A1B-3883B157121D}"/>
-    <hyperlink ref="A15" r:id="rId21" xr:uid="{F14DB676-86ED-4C4C-A82E-041A41111809}"/>
-    <hyperlink ref="A16" r:id="rId22" xr:uid="{ECD26114-AD89-4911-BC86-BD26FFA12A5B}"/>
-    <hyperlink ref="A18" r:id="rId23" xr:uid="{3DE72F04-773E-4312-BC3A-BAE2854A427A}"/>
-    <hyperlink ref="A22" r:id="rId24" xr:uid="{F455AB80-CB66-43BE-8398-CC28BD4FF81B}"/>
-    <hyperlink ref="A24" r:id="rId25" xr:uid="{83FD4BF5-2358-46C2-8D0C-96072593D040}"/>
-    <hyperlink ref="A25" r:id="rId26" xr:uid="{6507E877-B226-4C5B-8F8F-D66D9332E209}"/>
-    <hyperlink ref="A27" r:id="rId27" xr:uid="{5951487C-03AF-4F1F-8662-2C314FAEDD66}"/>
-    <hyperlink ref="A28" r:id="rId28" xr:uid="{A8221384-A48D-40A8-8C81-AC2AF6C7B442}"/>
-    <hyperlink ref="A29" r:id="rId29" xr:uid="{B97A3276-EC4E-49EA-8E07-10F5C0D21A0F}"/>
-    <hyperlink ref="A30" r:id="rId30" xr:uid="{B0B6F075-9800-4611-AECC-AA4AE46A87D0}"/>
+    <hyperlink ref="A8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="A23" r:id="rId4" xr:uid="{488F5B5B-FDA2-47E5-B070-D34C71D1EE05}"/>
+    <hyperlink ref="A19" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E388D481-4878-4695-9178-DAC43682E711}"/>
+    <hyperlink ref="A26" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg/1280px-Piet_Mondriaan%2C_1930_-_Mondrian_Composition_II_in_Red%2C_Blue%2C_and_Yellow.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B0491CE-5878-4284-9EB3-1CAE571073F5}"/>
+    <hyperlink ref="A9" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg/1280px-L%27Eiger%2C_le_M%C3%B6nch_et_la_Jungfrau_au-dessus_de_la_mer_de_brouillard_%281908%29_-_Ferdinand_Hodler_%28Mus%C3%A9e_Jenisch%2C_Vevey%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BA7F6A54-3B55-4CA1-913A-966DED893B72}"/>
+    <hyperlink ref="A31" r:id="rId8" xr:uid="{66617D80-66D1-4204-9086-F48C21B020E0}"/>
+    <hyperlink ref="A13" r:id="rId9" xr:uid="{0E4DF9FA-B9B4-434E-873D-8C7D7FD873BD}"/>
+    <hyperlink ref="A20" r:id="rId10" xr:uid="{98298F60-1A0B-47C9-96A2-DE89B59E8628}"/>
+    <hyperlink ref="A2" r:id="rId11" xr:uid="{464ECBC7-87A7-4781-8C5B-C632AEBADC12}"/>
+    <hyperlink ref="A3" r:id="rId12" xr:uid="{758CF4F1-880C-48E4-A2B1-204679A22EA7}"/>
+    <hyperlink ref="A4" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg/1280px-August_Macke_-_Market_in_Tunis_II_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{37043E81-17E6-42F7-9C6C-3086EC85D278}"/>
+    <hyperlink ref="A5" r:id="rId14" xr:uid="{A03D7D04-CD22-4203-8A15-2313E0EDEA52}"/>
+    <hyperlink ref="A6" r:id="rId15" xr:uid="{90C1B8BD-8BEB-4D69-9EBD-8740E75C8FEB}"/>
+    <hyperlink ref="A7" r:id="rId16" xr:uid="{A1FF0AEB-3C7F-46E9-A2F4-0748EB365A91}"/>
+    <hyperlink ref="A10" r:id="rId17" xr:uid="{D7963678-68E4-4022-A77F-33E8E5E51C37}"/>
+    <hyperlink ref="A11" r:id="rId18" xr:uid="{289B2CD7-ABF1-4282-9EC0-774C92EDE015}"/>
+    <hyperlink ref="A12" r:id="rId19" xr:uid="{F163392F-73C6-430A-8A1B-3883B157121D}"/>
+    <hyperlink ref="A15" r:id="rId20" xr:uid="{F14DB676-86ED-4C4C-A82E-041A41111809}"/>
+    <hyperlink ref="A16" r:id="rId21" xr:uid="{ECD26114-AD89-4911-BC86-BD26FFA12A5B}"/>
+    <hyperlink ref="A18" r:id="rId22" xr:uid="{3DE72F04-773E-4312-BC3A-BAE2854A427A}"/>
+    <hyperlink ref="A22" r:id="rId23" xr:uid="{F455AB80-CB66-43BE-8398-CC28BD4FF81B}"/>
+    <hyperlink ref="A24" r:id="rId24" xr:uid="{83FD4BF5-2358-46C2-8D0C-96072593D040}"/>
+    <hyperlink ref="A25" r:id="rId25" xr:uid="{6507E877-B226-4C5B-8F8F-D66D9332E209}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{5951487C-03AF-4F1F-8662-2C314FAEDD66}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{A8221384-A48D-40A8-8C81-AC2AF6C7B442}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{B97A3276-EC4E-49EA-8E07-10F5C0D21A0F}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{B0B6F075-9800-4611-AECC-AA4AE46A87D0}"/>
+    <hyperlink ref="A21" r:id="rId30" xr:uid="{603A479B-2712-41E9-9F99-1E3D83DA2E6D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-20e-niveau1.xlsx
+++ b/quizzes/peinture-20e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1680A64B-8F7B-4148-B584-310665B67C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0D8F54E-12D4-47F0-935B-B763EE1CF732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="223">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Modigliani_-_Nu_couch%C3%A9.jpg/1280px-Modigliani_-_Nu_couch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>60 × 92 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Pont_de_Charing_Cross%2C_par_Andr%C3%A9_Derain.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>81 × 100 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b5/Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg/1280px-Macke%2C_August_-_M%C3%A4dchen_unter_B%C3%A4umen_-_1914_-_2384_x_1773_px.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>119,5 × 159,5 cm</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg/1280px-Cha%C3%AFm_Soutine_-_Le_B%C5%93uf_%C3%A9corch%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>202 × 114 cm</t>
   </si>
   <si>
+    <t>biélorusse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/1280px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -157,6 +172,9 @@
     <t>91 × 73,5 cm</t>
   </si>
   <si>
+    <t>norvégienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -181,6 +199,9 @@
     <t>42,2 × 33,9 cm</t>
   </si>
   <si>
+    <t>autrichienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/Kirchner_1913_Street%2C_Berlin.jpg/1280px-Kirchner_1913_Street%2C_Berlin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -223,6 +244,9 @@
     <t>environ 68 × 80 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg/1920px-Le_M%C3%A9canicien_-_Fernand_L%C3%A9ger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -283,6 +307,9 @@
     <t>173,5 × 173 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Grant_Wood_-_American_Gothic_%281930%29.jpg/960px-Grant_Wood_-_American_Gothic_%281930%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -391,6 +418,9 @@
     <t>328 × 240 cm</t>
   </si>
   <si>
+    <t>suédoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg/1280px-Juan_Gris_-_Portrait_of_Pablo_Picasso_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -406,6 +436,9 @@
     <t>93,4 × 74,3 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/%D0%A7%D1%91%D1%80%D0%BD%D1%8B%D0%B9_%D1%81%D1%83%D0%BF%D1%80%D0%B5%D0%BC%D0%B0%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%B8%D0%B9_%D0%BA%D0%B2%D0%B0%D0%B4%D1%80%D0%B0%D1%82._1915._%D0%93%D0%A2%D0%93.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -427,6 +460,9 @@
     <t>79,5 × 79,5 cm</t>
   </si>
   <si>
+    <t>russe</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG/960px-Laszlo_moholy-nagy%2C_composizione_A.XX%2C_1924.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -448,6 +484,9 @@
     <t>dimensions non standardisées</t>
   </si>
   <si>
+    <t>hongroise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg/1280px-Maurice_Utrillo._La_Maison_de_Berlioz._1914.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -557,6 +596,9 @@
   </si>
   <si>
     <t>46 × 46 cm</t>
+  </si>
+  <si>
+    <t>hollandaise (Pays-Bas)</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg/1280px-Raoul_dufy%2C_la_fata_elettricit%C3%A0%2C_1937%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -1067,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -1080,7 +1122,7 @@
     <col min="8" max="8" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1105,785 +1147,878 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8">
         <v>1918</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>80</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>87</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>94</v>
+      </c>
+      <c r="I12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>103</v>
+      </c>
+      <c r="I13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>137</v>
+      </c>
+      <c r="I18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="5" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>145</v>
+      </c>
+      <c r="I19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>153</v>
+      </c>
+      <c r="I20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>166</v>
+      </c>
+      <c r="I22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C23" s="8">
         <v>1952</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>208</v>
+        <v>222</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
